--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>This is the correct live ICB Board landing (title 'ICB Board meetings | North East and North Cumbria NHS'). It is static-fetchable but does NOT hold PDFs directly, it is an index that lists upcoming meeting dates and links to one per-meeting sub-page for the most recent meeting plus a 'Previous Board meetings' archive. To reach current dated papers, follow the dated sub-page link (e.g. /board-meeting-held-in-public-on-tuesday-31-march-2026/), which contains the full PDF set (agenda, CEO report, finance, IDR, committee highlight reports) hosted under /media/&lt;hash&gt;/&lt;item&gt;.pdf. Crawler: fetch this landing, extract the dated sub-page(s) and the /previous-board-meetings/ page, then harvest the /media/*.pdf links on each. Coverage current (latest 31 Mar 2026; upcoming 16 Jun, 28 Jul, 29 Sep 2026). Filter out the separate ICP meetings link.</t>
+          <t>Landing lists upcoming ICB board meetings and links to 'Previous Board meetings' (/previous-board-meetings/), which enumerates dated meeting pages; each date links to a per-meeting page holding the papers. Crawler: landing -&gt; previous-board-meetings -&gt; dated meeting page -&gt; PDFs.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>/media/;board-in-public-agenda;ceo_board_report;icb-board;-board-march;item-</t>
+          <t>Board meeting held in public on [date];Integrated Care Board</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>integrated-care-partnership;icp;-icp-</t>
+          <t>extraordinary-meeting-only entries;committee agendas</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Landing indexes a dated sub-page (31 March 2026) carrying a full set of board PDFs under /media/.</t>
+          <t>Landing plus 'Previous Board meetings' sub-page list dated 2025/2026 ICB meetings, each with its own papers page. Papers reachable one click deep.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Coventry and Warwickshire ICB. The current URL is correct and live, but the happyhealthylives.uk host returns HTTP 403 to plain WebFetch (anti-bot, pattern E), which is why the validator flagged it broken. Loaded successfully under Playwright (location.host=www.happyhealthylives.uk): the page is a shared NHS Coventry &amp; Warwickshire / Herefordshire &amp; Worcestershire ICB Board site and renders current 2026 ICB Board content (CWHW ICB Board Governance Log 2026-27, draft public minutes 18 March 2026, 21 January 2026 papers). Per-meeting 'Meeting Papers' / agenda items are JS-driven accordions (anchors are href='#'); the underlying PDFs/xlsx live under /download/clientfiles/files/ and require JS expansion, so this is also pattern D (JS-needs-Playwright). This is the ICB Board (skip the separate ICP Meetings page). For HSJ purposes the CW and HW ICBs share this board infrastructure.</t>
+          <t>URL returns HTTP 403 to static fetchers (anti-bot/WAF on happyhealthylives.uk). URL is correct; a browser/Playwright session with a normal User-Agent reaches the ICB board meetings page and its dated packs.</t>
         </is>
       </c>
       <c r="N11" t="b">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>/download/clientfiles/files/Agenda%20&lt;NN&gt;%20CWHW%20...pdf;/download/clientfiles/files/...Governance%20Log%20&lt;YYYY-YY&gt;.xlsx;JS accordion 'Meeting Papers (part 1/2/3)' under each meeting date</t>
+          <t>Coventry and Warwickshire ICB Board meeting;ICB board papers</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ICP;ICP Meetings;Integrated Care Partnership;Committee;CAMHS Commissioning</t>
+          <t>happyhealthylives general health-content pages;committee meetings</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Page is 403 to WebFetch but loads in Playwright showing live 2026 CWHW ICB Board papers (Governance Log 2026-27, 18 March 2026 minutes); pack PDFs sit behind JS accordions.</t>
+          <t>happyhealthylives.uk WAF 403s static fetchers (matches the shallow connection-aborted flag) while the deep validator found papers. URL fine; needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The current URL IS correct and DOES surface dated board papers (title 'Board papers :: Herefordshire and Worcestershire Integrated Care System'); the validator's 1691-char read was a transient/partial render. The page shows only the NEXT/most-recent meeting (Wednesday 20 May 2026) with its agenda and item PDFs; the historical archive lives at the sibling page /meetings/past-board-papers (18 Mar 2026, 21 Jan 2026, 19 Nov 2025...). The actual document files are NOT on the icb.nhs.uk domain, they are served from the ICS document store at www.hwics.org.uk/download_file/&lt;id&gt;/463. Crawler should fetch both /meetings/board-papers (current) and /meetings/past-board-papers (archive) and harvest the hwics.org.uk/download_file links. Prefer the 'Agenda 00 Public Board &lt;date&gt;' PDF as the anchor. Papers may be branded 'CWHW' cluster but are still the H&amp;W ICB Board; do not confuse with the ICP or committee items.</t>
+          <t>Landing directly renders the current meeting's full pack (agenda, CEO report, finance, BAF, etc.) with 'Past Board Papers' and 'Past meetings' archive links in the nav. No JS gating; crawler reads PDF links straight from the page.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>hwics.org.uk/download_file/;Agenda 00 Public Board;CEO report;Public Board;Finance Plan</t>
+          <t>Agenda 00 Public Board;CEO report;Financial Plan &amp; Delivery;Risk Corp Objectives &amp; BAF;dated meeting</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>partnership;icp;Committee Escalation</t>
+          <t>ICS not ICB references;committee escalation-only</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Current URL surfaces the 20 May 2026 board pack; full archive at /meetings/past-board-papers, files hosted on hwics.org.uk.</t>
+          <t>Landing directly renders the current pack (9 files for 20 May 2026) with 'Past Board Papers' archive links. No JS gating. False positive.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.essex.icb.nhs.uk/publications/</t>
+          <t>https://www.essex.icb.nhs.uk/about/board/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1956,35 +1956,35 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The /publications/ index is the correct landing but does not list dated PDFs directly; it links to per-meeting publication sub-pages titled 'Essex ICB Board Meeting Pack &lt;date&gt;' (e.g. /publications/essex-icb-board-meeting-pack-23-april-2026/), each holding the actual board pack PDF at /wp-content/uploads/YYYY/MM/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;date&gt;.pdf. A crawler should fetch the publications index, follow links whose slug contains 'board-meeting-pack', then extract the wp-content/uploads PDF. Static fetch works (WordPress). Prefer the 'Part 1'/Part I public board pack PDF; ignore Part 2 (confidential) and any ICP/committee items. 2026 board packs live; older packs under earlier upload-month folders.</t>
+          <t>URL corrected from /publications/ to /about/board/ ('Integrated Care Board Meetings'), which routes to an events calendar (/events/category/board-and-committee-meetings/, dated meetings e.g. 16 Jul 2026) and a JS-filtered papers archive (/publications/?_publication_type=icb-board-meeting-papers). PDFs render only once the filter runs; needs Playwright.</t>
         </is>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>wp-content/uploads/YYYY/MM/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;date&gt;.pdf;/publications/essex-icb-board-meeting-pack-&lt;date&gt;/;Board Meeting Pack &lt;month&gt; &lt;year&gt;</t>
+          <t>ICB Board Meeting Papers;Essex ICB Board meeting;dated meeting</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Part-2;Part II;Integrated Care Partnership;ICP;committee;confidential</t>
+          <t>standalone policy documents;committee-only papers;ICP not ICB</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Confirmed live 23 April 2026 board pack PDF reachable from the publications index via a dated sub-page.</t>
+          <t>Old /publications/ was the generic publications archive (policies only, no board papers - the false-positive cause). Correct landing is /about/board/ which routes to dated meetings + a JS-filtered board-papers archive.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>This is the correct ICB Board landing; it lists upcoming and past board meeting dates (bi-monthly: e.g. 25 Nov 2025, 28 Jan 2026, 31 Mar 2026), each linking to a per-meeting sub-page under /board-meetings/north-east-london-icb-board-meeting-&lt;n&gt;/ (older under /events/). The actual board pack PDF is attached on the meeting sub-page once papers are published (5 working days before), served either as /wp-content/uploads/YYYY/MM/NHS-North-East-London-ICB-Board-&lt;dd.mm.yyyy&gt;.pdf or via /download-attachment/&lt;id&gt;. Crawl: fetch the landing, follow each board-meeting sub-page, extract the ICB Board pack PDF. Static fetch works (WordPress). Future meetings show only a Teams joining email until papers go live. Prefer the single combined 'NHS North East London ICB Board &lt;date&gt;' pack; exclude borough/place sub-committee, committees-in-common, partnership board, and ICP items.</t>
+          <t>Landing lists dated ICB board meetings; each meeting date IS the link to its pack ('click on the date to download the board papers'), published 5 working days before. Crawler follows landing -&gt; dated meeting link -&gt; PDF pack. Static fetch works.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>wp-content/uploads/YYYY/MM/NHS-North-East-London-ICB-Board-DD.MM.YYYY.pdf;/board-meetings/north-east-london-icb-board-meeting-&lt;n&gt;/;/download-attachment/&lt;id&gt;</t>
+          <t>North East London ICB Board Meeting;click on the date to download the board papers</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>sub-committee;committees-in-common;partnership-board;ICP;place;borough;Health and Wellbeing Board;your-area</t>
+          <t>committee meetings;future meetings with no papers yet</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Confirmed live ICB Board pack PDF (29 Jan 2025) via the WordPress uploads pattern reached from per-meeting sub-pages.</t>
+          <t>Board meetings page live with dated 2025/2026 meetings; papers download via the date links ('click on the date to download the board papers'). False-positive partial flag.</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Newly merged ICB (NHS North West London + NHS North Central London became NHS West and North London from 1 April 2026). The current board page is correct (rendered title 'West and North London ICB board meetings, agendas and papers') and is the canonical entry point. It lists future board dates (first board 17 Jun 2026, then 22 Jul 2026, 21 Oct 2026, 13 Jan 2027, 24 Mar 2027) and links to three document libraries: (1) its own new W+NL papers library at /how-we-are-run/policies-and-publications/navigate/479/2410 (a JS-rendered Joomla 'navigate' widget with dated folders per meeting), (2) legacy NCL papers at nclhealthandcare.org.uk, (3) legacy NWL papers at nwlondonicb.nhs.uk. Because the org only formed in April 2026, few/no current packs exist yet; new packs appear inside the dated folders of library 2410, which need rendering to expose PDF links. Crawl the navigate endpoint with a JS renderer, open each dated folder, take the combined board pack; for historical 2025 papers fall back to the two legacy domains. Exclude committee, primary care commissioning, and ICP/partnership material.</t>
+          <t>Landing ('NHS West and North London Board of Members') lists dated 2026/2027 meetings; each meeting links to papers in a JS document library (/policies-and-publications/navigate/479/2410#document-library-2410). Static fetch sees the link but the library renders client-side; needs Playwright. Ignore NCL/NWL legacy-archive links (predecessor orgs).</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -2321,27 +2321,27 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>/how-we-are-run/policies-and-publications/navigate/479/2410;navigate/479/2410/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;;dated 'Board meetings in public' folders;legacy: nwlondonicb.nhs.uk + nclhealthandcare.org.uk board papers</t>
+          <t>West and North London Board of Members;Papers available here;navigate/479/2410 document library</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>primary-care-commissioning-committee;Primary Care and Medicines Optimisation Committee;committee;ICP;partnership;public-meetings</t>
+          <t>legacy NCL/NWL archive links (predecessor orgs);future meetings with no papers yet</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Board page is the correct live landing and exposes a dated board-papers document library, but the PDFs sit inside a JS-rendered navigate widget (and legacy archives) so dated PDFs are not visible to a static fetch.</t>
+          <t>'Board of Members' lists dated 2026/2027 meetings; current meeting's papers sit in a JS document library (false-positive 'no papers visible'). Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>This is the correct ICB Board papers sub-page; the validator's 822-char 'near-empty' reading was a false negative. A normal fetch renders the Joomla document table, which lists dated 'Thames Valley ICB Board papers &lt;date&gt;' entries, each downloadable as a single combined PDF via /policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/&lt;id&gt;-thames-valley-icb-board-papers-&lt;date&gt;/file. The parent /board-papers page splits into 'NHS Thames Valley ICB' (current) and 'Pre-NHS Thames Valley archive' (older); use the former. Site resolves both with and without www. Crawl: fetch this sub-page, read the document table, follow each '.../file' link for the combined board papers PDF. Prefer the single 'ICB Board papers' combined PDF; exclude committee papers and any ICP items.</t>
+          <t>Landing directly lists the consolidated board pack PDF ('Thames Valley ICB Board papers {date}', ~2.8MB). One combined pack per meeting rather than many separate PDFs. Crawler reads the single dated pack link. Static fetch works.</t>
         </is>
       </c>
       <c r="N29" t="b">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>/policies-and-documents/how-we-make-decisions/board-papers/nhs-thames-valley-icb/&lt;id&gt;-thames-valley-icb-board-papers-&lt;date&gt;/file;Thames Valley ICB Board papers &lt;month&gt; &lt;year&gt;</t>
+          <t>Thames Valley ICB Board papers [date];single consolidated PDF</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>pre-nhs-thames-valley-archive;committee;ICP;Integrated Care Partnership</t>
+          <t>policy/how-we-make-decisions sibling docs;committee papers</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Confirmed live 20 May 2026 combined board papers PDF (2.81 MB) listed in the rendered document table on the current sub-page.</t>
+          <t>Landing directly lists the consolidated board pack PDF (e.g. 20 May 2026, ~2.8MB). 'Thin' because Thames Valley publishes one combined pack per meeting, not broken.</t>
         </is>
       </c>
     </row>
@@ -3005,25 +3005,25 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered). A static fetch of the 'Meetings in public' page returns a near-empty body; under headless Chromium it renders on cios.icb.nhs.uk (verify location.host — the shared browser drifts to other workers' pages) at ~4KB of content and exposes the ICB Board papers. The page surfaces (a) direct dated ICB Board PDFs for the current FY hosted on a SEPARATE document-library subdomain docs.cios.icb.nhs.uk, and (b) per-FY year-archive sub-pages /about/meetings/2025-to-2026-papers/, /2024-to-2025-papers/, /2023-to-2024-papers/, /2022-to-2023-papers/. The 2025-to-2026-papers archive page (also JS-rendered) lists each ICB Board meeting's papers itemised per agenda item (NOT a single combined pack) at docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{FY}/{YYYYMM}/ (FY = 2526, YYYYMM = meeting month), e.g. AgendaPart1ICBBoardMay2025.pdf and ICB{seq}*.pdf reports. A crawler should anchor each meeting on the 'Agenda Part 1 ICB Board {Month} {Year}' PDF and gather the sibling ICB{seq} files in the same {YYYYMM} folder. Some links are wrapped in Outlook safelinks redirects (unwrap via url= param). Static fetch misses all of this. Filter to the ICB Board only — EXCLUDE the Integrated Care Partnership (/ics/icp/) and the South West Peninsula ICB-cluster page (/icb-cluster/).</t>
+          <t>'Meetings in public' lists CIOS-specific dated ICB papers (e.g. 28 May 2026 extraordinary, AGM) and references the South West Peninsula joint board (swpboard.nhs.uk, see QJK) for most routine governance. Crawler reads dated PDF links from the page. Static fetch works.</t>
         </is>
       </c>
       <c r="N36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>/about/meetings/{YYYY}-to-{YYYY}-papers/ year-archive sub-pages;docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{FY}/{YYYYMM}/*.pdf;anchor meeting on AgendaPart1ICBBoard{Month}{Year}.pdf, gather sibling ICB{seq}*.pdf in same folder;FY folder is 4-digit (2526); papers are itemised per agenda item, not one combined pack;unwrap gbr01.safelinks.protection.outlook.com via url= query parameter</t>
+          <t>NHS CIOS ICB meeting in public;Extraordinary Meeting;AGM;South West Peninsula Board</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>/ics/icp/ (Integrated Care Partnership);/icb-cluster/ (South West Peninsula ICB cluster board);BoardQuestionsAndSupportingInformation (public questions, not board packs);youtube.com playlist links;language/translate anchors (#)</t>
+          <t>DOI register-only;AGM-minutes-only;Annual Report</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>The 2025-to-2026 archive rendered dated ICB Board papers for May 2025, July 2025 and an Extraordinary meeting (Aug 2025 / May 2026) under BoardMeetings/2526/{YYYYMM}/ on docs.cios.icb.nhs.uk, distinct from ICP/committee content.</t>
+          <t>cios.icb.nhs.uk/about/meetings/ live with dated 2025/2026 CIOS papers and pointer to the SW Peninsula joint board. Not broken.</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pattern C + cluster (SW-PEN). NHS Devon and NHS Cornwall &amp; Isles of Scilly delegated their board functions to the joint South West Peninsula Board (Sept 2025); the joint board pack now lives on swpboard.nhs.uk, not devon.icb.nhs.uk (old /nhs-devon-board/meetings-and-papers/ is HTTP 404). Landing lists dated meetings (e.g. 16 Oct 2025, 27 Nov 2025, 29 Jan 2026) with a 'View the meeting papers and minutes' link per meeting leading to the combined pack PDF under /wp-content/uploads/YYYY/MM/ (e.g. SWPB-Public-29.01.2026-Meeting-Papers.pdf). This pack covers BOTH Devon and Cornwall &amp; IoS. URL fixed 2026-06-13.</t>
+          <t>swpboard.nhs.uk is the live joint SW Peninsula cluster home (titled 'NHS CIOS and Devon ICB'). Landing lists dated joint board meetings; each links to the shared papers index /board-meetings/board-meeting-papers-and-minutes/. Crawler: landing -&gt; papers-and-minutes index -&gt; dated packs. Static fetch works.</t>
         </is>
       </c>
       <c r="N37" t="b">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>SWPB-Public-DD.MM.YYYY-Meeting-Papers.pdf;South West Peninsula Board Meeting in Public;View the meeting papers and minutes</t>
+          <t>NHS CIOS and Devon ICB;South West Peninsula Board;View the meeting papers and minutes</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>committee/sub-committee papers;minutes only;legacy devon.icb.nhs.uk standalone pages</t>
+          <t>YouTube livestream;single-ICB CIOS-only extraordinary</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Joint SW Peninsula Board on swpboard.nhs.uk lists 2025/26 meetings incl 29 Jan 2026 (SWPB-Public-29.01.2026-Meeting-Papers.pdf); old devon.icb.nhs.uk path is 404.</t>
+          <t>swpboard.nhs.uk is the live joint home for the South West Peninsula cluster ('NHS CIOS and Devon ICB') with dated 2025-2027 meetings. Not broken - expected cluster home.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Landing lists upcoming ICB board meetings and links to 'Previous Board meetings' (/previous-board-meetings/), which enumerates dated meeting pages; each date links to a per-meeting page holding the papers. Crawler: landing -&gt; previous-board-meetings -&gt; dated meeting page -&gt; PDFs.</t>
+          <t>The landing page is a hub: it links to the latest 'Board meeting held in public on &lt;date&gt;' sub-page plus a 'Previous Board meetings' index. Each meeting sub-page (e.g. .../board-meeting-held-in-public-on-tuesday-31-march-2026/) carries the full set of per-item ICB Board PDFs served from /media/&lt;hash&gt;/&lt;filename&gt;.pdf (agenda, draft minutes, action log, CEO report, committee highlight reports, finance/delivery reports). Meetings are bi-monthly. To crawl: open the ICB hub, follow the latest meeting sub-page and the Previous Board meetings index, then collect the /media/ PDFs. Files are clearly 'board-in-public' / 'icb board', so ICP and standalone committee meetings are not mixed in.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Board meeting held in public on [date];Integrated Care Board</t>
+          <t>sub-page slug 'board-meeting-held-in-public-on-&lt;weekday&gt;-&lt;dd&gt;-&lt;month&gt;-&lt;year&gt;';PDFs under /media/&lt;hash&gt;/ named with 'board-in-public' or 'item-NN-...board';agenda file '&lt;yyyymmdd&gt;-board-in-public-agenda.pdf'</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>extraordinary-meeting-only entries;committee agendas</t>
+          <t>ICP;Integrated Care Partnership;Joint Committee;exec-cttee minutes (when standalone)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Landing plus 'Previous Board meetings' sub-page list dated 2025/2026 ICB meetings, each with its own papers page. Papers reachable one click deep.</t>
+          <t>Upgraded from papers_partial: the 31 March 2026 ICB Board sub-page exposes the full agenda plus ~20 dated board paper PDFs on-domain.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>URL returns HTTP 403 to static fetchers (anti-bot/WAF on happyhealthylives.uk). URL is correct; a browser/Playwright session with a normal User-Agent reaches the ICB board meetings page and its dated packs.</t>
+          <t>Current URL is correct and live; the reported failure is a WAF/bot 403 that only blocks WebFetch — load it in Playwright (page title 'ICB Board Meetings - Happy Healthy Lives' confirms). The org now runs as the CWHW cluster (Coventry &amp; Warwickshire + Herefordshire &amp; Worcestershire), so packs are labelled 'CWHW ICB Board' or 'CWICB Board'. Meeting papers sit inside JavaScript accordions per meeting date whose individual PDF links load dynamically on expand; the real files live at /download/clientfiles/files/. Google site:happyhealthylives.uk with the file path is the fastest way to surface a specific pack URL.</t>
         </is>
       </c>
       <c r="N11" t="b">
@@ -1184,27 +1184,27 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Coventry and Warwickshire ICB Board meeting;ICB board papers</t>
+          <t>/download/clientfiles/files/ host path for all packs;Filenames like 'Papers for the {DD} {Mon} {YYYY} CWICB Board meeting';'CWHW ICB Board' prefix on cluster governance docs;Often split into PACK 1 / PACK 2 / PACK 3;Accordion grouped by meeting date on the landing page</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>happyhealthylives general health-content pages;committee meetings</t>
+          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee Escalation;Herefordshire &amp; Worcestershire-only board</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>happyhealthylives.uk WAF 403s static fetchers (matches the shallow connection-aborted flag) while the deep validator found papers. URL fine; needs Playwright.</t>
+          <t>Live landing page confirmed via Playwright with dated 2026 board entries and a recent example pack (19 Nov 2025 CWICB Board meeting papers) on-domain.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Landing directly renders the current meeting's full pack (agenda, CEO report, finance, BAF, etc.) with 'Past Board Papers' and 'Past meetings' archive links in the nav. No JS gating; crawler reads PDF links straight from the page.</t>
+          <t>The current /meetings/board-papers URL works and shows the upcoming/most-recent public Board meeting's individual agenda-item PDFs (e.g. 20 May 2026: Agenda 00 Public Board, CEO report, Delivery &amp; Quality Report, etc.). Historical meetings live at /meetings/past-board-papers, which lists every ICB Board meeting back to July 2022 with download links served from the hwics.org.uk file store (download_file/&lt;id&gt;/463). Both pages are explicitly 'ICB Board' / 'Public Board' and are the correct (non-ICP, non-committee) target. Crawl /meetings/board-papers for current packs and /meetings/past-board-papers for the archive.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Agenda 00 Public Board;CEO report;Financial Plan &amp; Delivery;Risk Corp Objectives &amp; BAF;dated meeting</t>
+          <t>title 'Agenda 00 Public Board &lt;date&gt;' or 'Agenda - ICB Board - &lt;dd-mm-yyyy&gt;';per-item PDFs prefixed 'Agenda NN';archive download links https://www.hwics.org.uk/download_file/&lt;id&gt;/463</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ICS not ICB references;committee escalation-only</t>
+          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee minutes</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Landing directly renders the current pack (9 files for 20 May 2026) with 'Past Board Papers' archive links. No JS gating. False positive.</t>
+          <t>Current page lists nine dated 20 May 2026 ICB Board documents and the past-papers page lists ICB Board agendas back to 2022.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.essex.icb.nhs.uk/about/board/</t>
+          <t>https://www.essex.icb.nhs.uk/publications/?search=&amp;type=icb-board-meeting-papers&amp;date_from=#filter-summary</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1956,35 +1956,35 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>URL corrected from /publications/ to /about/board/ ('Integrated Care Board Meetings'), which routes to an events calendar (/events/category/board-and-committee-meetings/, dated meetings e.g. 16 Jul 2026) and a JS-filtered papers archive (/publications/?_publication_type=icb-board-meeting-papers). PDFs render only once the filter runs; needs Playwright.</t>
+          <t>The /about/board/ page has no papers; the working route is the Publications archive filtered by type 'icb-board-meeting-papers'. That filtered listing returns detail pages titled 'Essex ICB Board Meeting Pack &lt;day month year&gt;' (e.g. 23 April 2026, 1 April 2026). Each detail page links to a single combined 'Part 1 Essex ICB Board Meeting Pack' PDF hosted under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/. To crawl: load the filtered publications URL, follow each /publications/essex-icb-board-meeting-pack-*/ detail page, then grab the wp-content/uploads PDF. Filtering by the type slug excludes ICP and committee items automatically.</t>
         </is>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>ICB Board Meeting Papers;Essex ICB Board meeting;dated meeting</t>
+          <t>/publications/essex-icb-board-meeting-pack-&lt;day&gt;-&lt;month&gt;-&lt;year&gt;/;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;day&gt;-&lt;Month&gt;-&lt;Year&gt;.pdf;title contains 'Essex ICB Board Meeting Pack'</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>standalone policy documents;committee-only papers;ICP not ICB</t>
+          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee meeting papers</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Old /publications/ was the generic publications archive (policies only, no board papers - the false-positive cause). Correct landing is /about/board/ which routes to dated meetings + a JS-filtered board-papers archive.</t>
+          <t>Filtered publications listing shows dated 2026 board packs, each resolving to a downloadable combined PDF (8MB confirmed for 23 April 2026).</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Landing lists dated ICB board meetings; each meeting date IS the link to its pack ('click on the date to download the board papers'), published 5 working days before. Crawler follows landing -&gt; dated meeting link -&gt; PDF pack. Static fetch works.</t>
+          <t>Fetch this landing page (loads fine via WebFetch, no WAF). It lists 'North East London ICB Board Meeting' entries (upcoming + past), each linking to an individual meeting page at /board-meetings/north-east-london-icb-board-meeting-{N}/. Open the most recent past meeting page and grab the single combined paper-pack PDF served from /download-attachment/{id} (labelled e.g. 'NHS North East London ICB Board - 20 May 2026'). Board meets bi-monthly. Ignore the many sub-committee, partnership board, place-based (borough) and ICP entries that also appear under /board-meetings/ — only 'North East London ICB Board Meeting' is the ICB Board.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>North East London ICB Board Meeting;click on the date to download the board papers</t>
+          <t>/board-meetings/north-east-london-icb-board-meeting-{N}/;/download-attachment/{id};'NHS North East London ICB Board - {DD Month YYYY}'</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>committee meetings;future meetings with no papers yet</t>
+          <t>ICP;Integrated Care Partnership;Sub-committee;Partnership Board;Primary Care Contracts;Health and Care Board</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Board meetings page live with dated 2025/2026 meetings; papers download via the date links ('click on the date to download the board papers'). False-positive partial flag.</t>
+          <t>Landing page lists ICB Board meetings; individual meeting page (20 May 2026) serves a 3MB combined board pack PDF.</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Landing ('NHS West and North London Board of Members') lists dated 2026/2027 meetings; each meeting links to papers in a JS document library (/policies-and-publications/navigate/479/2410#document-library-2410). Static fetch sees the link but the library renders client-side; needs Playwright. Ignore NCL/NWL legacy-archive links (predecessor orgs).</t>
+          <t>New W&amp;NL site live from 1 April 2026 (merger of NW London + North Central London). The board-meetings page lists ICB Board of Members dates (1 Apr, 17 Jun, 22 Jul, 23 Sep AGM, 21 Oct 2026, 27 Jan, 24 Mar 2027) and links to the papers via the document library at /how-we-are-run/policies-and-publications/navigate/479/2410 (folder 'Board meetings in public'). WebFetch sees the library shell but NOT the folder contents (JS-rendered) — use Playwright to open each per-meeting date folder where the individual PDFs live (agenda, appointments paper, constitution, governance, SFIs etc.), each served from /download_file/{uuid}/{n}. Predecessor packs are at nclhealthandcare.org.uk and nwlondonicb.nhs.uk but the live on-domain source is the document library. Board meets quarterly. Exclude the '29 June 2026 PCCG' folder (Primary Care Commissioning Group, not the Board) and the ICP.</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>West and North London Board of Members;Papers available here;navigate/479/2410 document library</t>
+          <t>/how-we-are-run/policies-and-publications/navigate/479/2410 (Board meetings in public folder);per-meeting date subfolders e.g. /navigate/480/2410 = 1 April 2026;individual PDFs at /download_file/{uuid}/{n};'{YYYY.MM.DD} West and North London ICB Board ...'</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>legacy NCL/NWL archive links (predecessor orgs);future meetings with no papers yet</t>
+          <t>ICP;Integrated Care Partnership;PCCG;Primary Care Commissioning;Primary Care and Medicines Optimisation Committee;Committee</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>'Board of Members' lists dated 2026/2027 meetings; current meeting's papers sit in a JS document library (false-positive 'no papers visible'). Needs Playwright.</t>
+          <t>Document library 'Board meetings in public' &gt; 1 April 2026 folder contains the ICB Board agenda, appointments paper, constitution, governance and SFI PDFs (download_file links).</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Landing directly lists the consolidated board pack PDF ('Thames Valley ICB Board papers {date}', ~2.8MB). One combined pack per meeting rather than many separate PDFs. Crawler reads the single dated pack link. Static fetch works.</t>
+          <t>Fetch this page directly (WebFetch works, no WAF). It is the Thames Valley ICB board papers listing; each entry is a single combined 'Public Board pack' PDF named 'Thames Valley ICB Board papers from {Month YYYY}' with a download link. Newest present is May 2026 (pack dated 13 May 2026 for the 20 May 2026 meeting). Grab the top/most-recent PDF. This is the ICB Board; do not confuse with any committee pages elsewhere under /how-we-make-decisions/.</t>
         </is>
       </c>
       <c r="N29" t="b">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Thames Valley ICB Board papers [date];single consolidated PDF</t>
+          <t>'Thames Valley ICB Board papers from {Month YYYY}';single combined Public Board pack PDF per meeting</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>policy/how-we-make-decisions sibling docs;committee papers</t>
+          <t>ICP;Integrated Care Partnership;Committee;Joint Committee</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Landing directly lists the consolidated board pack PDF (e.g. 20 May 2026, ~2.8MB). 'Thin' because Thames Valley publishes one combined pack per meeting, not broken.</t>
+          <t>Page lists the May 2026 Thames Valley ICB Board pack (2.81MB PDF) for the 20 May 2026 public board meeting.</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>'Meetings in public' lists CIOS-specific dated ICB papers (e.g. 28 May 2026 extraordinary, AGM) and references the South West Peninsula joint board (swpboard.nhs.uk, see QJK) for most routine governance. Crawler reads dated PDF links from the page. Static fetch works.</t>
+          <t>The current URL is in fact live and correct (last reviewed 27 May 2026) — the reported breakage did not reproduce; WebFetch returns it cleanly. Reach it via About Us &gt; Meetings. Packs are grouped by financial year (2025-26, 2024-25, etc.) with direct PDFs hosted on a separate docs subdomain at docs.cios.icb.nhs.uk/DocumentsLibrary/NHSCornwallAndIslesOfScilly/Organisation/PublicMeetings/BoardMeetings/{YYYY}/{YYYYMM}/. The ICB now operates in a cluster with NHS Devon, and recent sessions are 'Extraordinary' or AGM, but the board pack is published on its own cios.icb.nhs.uk domain.</t>
         </is>
       </c>
       <c r="N36" t="b">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>NHS CIOS ICB meeting in public;Extraordinary Meeting;AGM;South West Peninsula Board</t>
+          <t>docs.cios.icb.nhs.uk/DocumentsLibrary/.../BoardMeetings/{fy e.g. 2526}/{yyyymm}/ path;Separate PDFs per item: Agenda, DOI Register, Minutes, individual reports;Filenames like Agenda...{Month}{Year}.pdf;Grouped by financial year on the landing page</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOI register-only;AGM-minutes-only;Annual Report</t>
+          <t>Integrated Care Partnership;ICP;Joint Committee;Cluster governance committee</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>cios.icb.nhs.uk/about/meetings/ live with dated 2025/2026 CIOS papers and pointer to the SW Peninsula joint board. Not broken.</t>
+          <t>Live page lists 2022-23 through 2025-26 board packs with direct PDF agenda/DOI/report links on the official docs subdomain.</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://swpboard.nhs.uk/board-meetings/</t>
+          <t>https://onedevon.org.uk/nhs-devon/nhs-devon-board/meeting-papers-and-minutes/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>swpboard.nhs.uk is the live joint SW Peninsula cluster home (titled 'NHS CIOS and Devon ICB'). Landing lists dated joint board meetings; each links to the shared papers index /board-meetings/board-meeting-papers-and-minutes/. Crawler: landing -&gt; papers-and-minutes index -&gt; dated packs. Static fetch works.</t>
+          <t>The old swpboard.nhs.uk cluster URL is dead; the live board-papers archive is now on NHS Devon's primary domain at onedevon.org.uk/nhs-devon/nhs-devon-board/meeting-papers-and-minutes/ (reachable from homepage nav: NHS Devon &gt; NHS Devon Board &gt; Meeting Papers and Minutes). WebFetch works on this domain (no WAF). Each meeting has an 'Agenda and Papers' download plus separate 'Minutes'; files resolve through /download/ slug redirects (wpdmdl) to wp-content PDFs. A mirror page exists at devon.icb.nhs.uk/nhs-devon-board/meetings-and-papers/. Note the ICB now sits in a CIOS+Devon cluster, but the Devon board pack is published here.</t>
         </is>
       </c>
       <c r="N37" t="b">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>NHS CIOS and Devon ICB;South West Peninsula Board;View the meeting papers and minutes</t>
+          <t>onedevon.org.uk/download/nhs-devon-board-agenda-and-papers-{dd}-{month}-{yyyy}/ slug redirects;'Agenda and Papers' = full pack; separate 'Minutes' files;WordPress wpdmdl download-manager IDs;Bi-monthly cadence (Jan/Mar/May/Jul/Sep/Nov);Labelled 'NHS Devon Board Meeting'</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>YouTube livestream;single-ICB CIOS-only extraordinary</t>
+          <t>ICP;Integrated Care Partnership;Joint Committee;Local Care Partnership</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>swpboard.nhs.uk is the live joint home for the South West Peninsula cluster ('NHS CIOS and Devon ICB') with dated 2025-2027 meetings. Not broken - expected cluster home.</t>
+          <t>Archive lists full ICB Board agenda/papers and minutes through 28 Aug 2025 with on-domain download links.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Upgraded from papers_partial: the 31 March 2026 ICB Board sub-page exposes the full agenda plus ~20 dated board paper PDFs on-domain.</t>
+          <t>NENC ICB meetings hub live; latest 16 June 2026 extraordinary + previous meetings index; per-item PDFs under /media. Validator saw hub only.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Current page lists nine dated 20 May 2026 ICB Board documents and the past-papers page lists ICB Board agendas back to 2022.</t>
+          <t>H&amp;W ICB board-papers page live (latest public meeting 20 May 2026); past-board-papers archive back to 2022.</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Sibling 'meeting-papers' page lists full 2025-2026 DLN/DDICB board packs via /download/ redirects to PDFs on the same domain.</t>
+          <t>Derby &amp; Derbyshire ICB meeting-papers archive confirmed live via search (papers 2020-2026, DLN meets-in-common); 503 to automated fetch is WAF.</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Filtered publications listing shows dated 2026 board packs, each resolving to a downloadable combined PDF (8MB confirmed for 23 April 2026).</t>
+          <t>Essex ICB publications filtered to ICB board meeting papers; latest 'Essex ICB Board Meeting Pack' 23 April 2026.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Landing page lists ICB Board meetings; individual meeting page (20 May 2026) serves a 3MB combined board pack PDF.</t>
+          <t>NE London ICB board meetings &amp; papers page live; per-meeting packs via /download-attachment; papers publish 5 working days before meeting.</t>
         </is>
       </c>
     </row>
@@ -2331,17 +2331,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Document library 'Board meetings in public' &gt; 1 April 2026 folder contains the ICB Board agenda, appointments paper, constitution, governance and SFI PDFs (download_file links).</t>
+          <t>W&amp;NL ICB board meetings page live (dates to Mar 2027); papers in JS-rendered document library - needs browser.</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Page lists the May 2026 Thames Valley ICB Board pack (2.81MB PDF) for the 20 May 2026 public board meeting.</t>
+          <t>Thames Valley ICB board papers listing live; latest 20 May 2026 combined public board pack.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The landing page is a hub: it links to the latest 'Board meeting held in public on &lt;date&gt;' sub-page plus a 'Previous Board meetings' index. Each meeting sub-page (e.g. .../board-meeting-held-in-public-on-tuesday-31-march-2026/) carries the full set of per-item ICB Board PDFs served from /media/&lt;hash&gt;/&lt;filename&gt;.pdf (agenda, draft minutes, action log, CEO report, committee highlight reports, finance/delivery reports). Meetings are bi-monthly. To crawl: open the ICB hub, follow the latest meeting sub-page and the Previous Board meetings index, then collect the /media/ PDFs. Files are clearly 'board-in-public' / 'icb board', so ICP and standalone committee meetings are not mixed in.</t>
+          <t>Static WebFetch works - no JS. The landing lists upcoming ICB Board dates and links the current/most-recent public board pack as a single PDF under /media/, plus a 'Previous Board meetings' sub-page (/about-us/corporate-information/governance/meetings-and-agendas/previous-board-meetings/) for the historical archive. This is the ICB Board (not ICP). Read the main page for the latest pack and follow the previous-meetings link for prior packs. Deep validator flagged it because only one PDF is exposed on the top page at a time.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>sub-page slug 'board-meeting-held-in-public-on-&lt;weekday&gt;-&lt;dd&gt;-&lt;month&gt;-&lt;year&gt;';PDFs under /media/&lt;hash&gt;/ named with 'board-in-public' or 'item-NN-...board';agenda file '&lt;yyyymmdd&gt;-board-in-public-agenda.pdf'</t>
+          <t>/media/ path;filename YYYYMMDD-public-board-pdf-pack.pdf;'public board';'Board Papers'</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Joint Committee;exec-cttee minutes (when standalone)</t>
+          <t>integrated care partnership;ICP;committee;sub-committee</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>NENC ICB meetings hub live; latest 16 June 2026 extraordinary + previous meetings index; per-item PDFs under /media. Validator saw hub only.</t>
+          <t>Page hosts a dated ICB board pack (16 June 2026) plus a 'Previous Board meetings' archive link, so the current URL is live and correct.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The current /meetings/board-papers URL works and shows the upcoming/most-recent public Board meeting's individual agenda-item PDFs (e.g. 20 May 2026: Agenda 00 Public Board, CEO report, Delivery &amp; Quality Report, etc.). Historical meetings live at /meetings/past-board-papers, which lists every ICB Board meeting back to July 2022 with download links served from the hwics.org.uk file store (download_file/&lt;id&gt;/463). Both pages are explicitly 'ICB Board' / 'Public Board' and are the correct (non-ICP, non-committee) target. Crawl /meetings/board-papers for current packs and /meetings/past-board-papers for the archive.</t>
+          <t>Static WebFetch works. The landing (herefordshireandworcestershire.icb.nhs.uk/meetings/board-papers) renders the itemised agenda for the next/most-recent public board meeting, but the individual document files are hosted on the cluster/partner domain www.hwics.org.uk via /download_file/{id} URLs (H&amp;W is clustered with Coventry &amp; Warwickshire; the 15 July 2026 pack is a joint 'in common' board carrying both CW and HW annual reports). This is acceptable and is the ICB Board (not ICP). Scrape the .icb.nhs.uk/meetings/board-papers page for agenda item links, which resolve to hwics.org.uk download URLs. Coverage 2026; prior meetings reachable from the same meetings area. Prefer this H&amp;W ICB page as the entry point.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>title 'Agenda 00 Public Board &lt;date&gt;' or 'Agenda - ICB Board - &lt;dd-mm-yyyy&gt;';per-item PDFs prefixed 'Agenda NN';archive download links https://www.hwics.org.uk/download_file/&lt;id&gt;/463</t>
+          <t>'Public Board';'Agenda 0x';hwics.org.uk/download_file/;'CEO report';'BAF';'Financial Report'</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee minutes</t>
+          <t>integrated care partnership;ICP;committee escalation-only;place-based</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>H&amp;W ICB board-papers page live (latest public meeting 20 May 2026); past-board-papers archive back to 2022.</t>
+          <t>Page lists a full dated agenda for the 15 July 2026 public ICB Board (CEO report, finance, BAF, annual reports), confirming a live board-papers archive at the current URL.</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.hertsandwestessex.ics.nhs.uk/documents/?location=all&amp;type=board-papers&amp;cat=all&amp;date=</t>
+          <t>https://www.centraleast.icb.nhs.uk/documents/?location=all&amp;type=board-papers&amp;cat=all&amp;date=</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Pattern C/F: the configured /about/icb/board/ landing only links to members and a meetings-in-public overview with no dated PDFs, so the working URL is the board-papers document archive (type=board-papers), which lists one per-meeting document page per ICB Board meeting in public on the org's own domain. Each per-meeting page (slug 'papers-for-the-integrated-care-board-meeting-in-public-&lt;weekday&gt;-&lt;date&gt;') holds that meeting's pack. NOTE: this org is recorded under the new Central East ICB ODS code (S1Y5D) but still publishes on its legacy Herts and West Essex ICS domain (hertsandwestessex.ics.nhs.uk); the board moved from bi-monthly to quarterly from April 2025, so meetings are sparse (latest 6 Feb 2026). Use the per-meeting document page as the meeting URL and take the combined board pack; exclude Primary Care Transformation Committee papers.</t>
+          <t>Central East ICB (live 1 April 2026, merger of Herts &amp; West Essex, BLMK and Cambridgeshire &amp; Peterborough ICBs) has its own domain centraleast.icb.nhs.uk. The old hertsandwestessex URL 301s to centraleast.icb.nhs.uk/ but loses the /documents/ path, landing on the homepage with no papers. The correct live page is the same document filter on the new domain (/documents/?location=all&amp;type=board-papers&amp;cat=all&amp;date=), listing 'Integrated Board meeting in public' packs (their name for the ICB Board, not ICP). Each result is an HTML document-detail page (e.g. /documents/papers-for-the-integrated-board-meeting-in-public-26-june-2026/) holding the PDFs, so crawl the filter list then open each detail page. Static fetch works. Coverage April 2026 and June 2026 (new org).</t>
         </is>
       </c>
       <c r="N20" t="b">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>papers-for-the-integrated-care-board-meeting-in-public;/documents/;ICB Board category</t>
+          <t>'Papers for the Integrated Board meeting in public {date}';'Public Questions for Central East ICB Board';/documents/ detail pages;type=board-papers filter</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Primary Care Transformation;Committee;ICP;AGM</t>
+          <t>ICP / Integrated Care Partnership;predecessor hertsandwestessex/BLMK/CPICS pages;committee-only</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Board-papers archive lists dated ICB-Board-categorised meeting packs through 6 February 2026 on the org's own domain.</t>
+          <t>Predecessor hertsandwestessex.ics.nhs.uk URL 301-redirects to the Central East homepage (path dropped); the equivalent filter on the new centraleast.icb.nhs.uk domain lists dated Integrated Board packs for 1 April 2026 and 26 June 2026.</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The /about/board/ page has no papers; the working route is the Publications archive filtered by type 'icb-board-meeting-papers'. That filtered listing returns detail pages titled 'Essex ICB Board Meeting Pack &lt;day month year&gt;' (e.g. 23 April 2026, 1 April 2026). Each detail page links to a single combined 'Part 1 Essex ICB Board Meeting Pack' PDF hosted under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/. To crawl: load the filtered publications URL, follow each /publications/essex-icb-board-meeting-pack-*/ detail page, then grab the wp-content/uploads PDF. Filtering by the type slug excludes ICP and committee items automatically.</t>
+          <t>This is the correct NHS Essex (new post-April-2026 ICB) board-papers archive. The URL is a pre-applied publications filter (type=icb-board-meeting-papers) that, despite looking like a JS/AJAX search, returns populated server-rendered results on static fetch. Each result is a publication landing page (e.g. /publications/essex-icb-board-meeting-pack-23-april-2026/) which hosts the downloadable board-pack PDF. Hit the filter URL, collect the /publications/...-board-meeting-pack-&lt;date&gt;/ links, then follow each to the PDF. Brand-new ICB so coverage starts 1 April 2026; the list will grow. Static fetch works, Playwright not required.</t>
         </is>
       </c>
       <c r="N21" t="b">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>/publications/essex-icb-board-meeting-pack-&lt;day&gt;-&lt;month&gt;-&lt;year&gt;/;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Part-1-Essex-ICB-Board-Meeting-Pack-&lt;day&gt;-&lt;Month&gt;-&lt;Year&gt;.pdf;title contains 'Essex ICB Board Meeting Pack'</t>
+          <t>type=icb-board-meeting-papers;'Board Meeting Pack';/publications/essex-icb-board-meeting-pack-&lt;date&gt;/;'Showing N Publications filtered by ICB Board Meeting Papers'</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>ICP Board;Integrated Care Partnership;Joint Committee;Committee meeting papers</t>
+          <t>ICP / Integrated Care Partnership;committee papers;non-board publication types</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Essex ICB publications filtered to ICB board meeting papers; latest 'Essex ICB Board Meeting Pack' 23 April 2026.</t>
+          <t>Static fetch returned 'Showing 2 Publications filtered by ICB Board Meeting Papers' with two dated 2026 packs (Essex ICB Board Meeting Pack 23 April 2026 and 1 April 2026); the filter renders server-side.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Fetch this landing page (loads fine via WebFetch, no WAF). It lists 'North East London ICB Board Meeting' entries (upcoming + past), each linking to an individual meeting page at /board-meetings/north-east-london-icb-board-meeting-{N}/. Open the most recent past meeting page and grab the single combined paper-pack PDF served from /download-attachment/{id} (labelled e.g. 'NHS North East London ICB Board - 20 May 2026'). Board meets bi-monthly. Ignore the many sub-committee, partnership board, place-based (borough) and ICP entries that also appear under /board-meetings/ — only 'North East London ICB Board Meeting' is the ICB Board.</t>
+          <t>This is the correct ICB Board landing (explicitly the ICB, not ICP). The main page lists dated board meetings (roughly every other month) but the PDFs are not on the landing itself - each date links to an individual event page under /events/board-meetings-and-papers-&lt;n&gt;/ which hosts the dated board-pack PDF. Scrape the landing for dated meeting links, follow each into its event page, then grab the PDF pack. Static fetch of the event pages does expose the PDF, so Playwright is not strictly required, though the landing's date links must be followed. Exclude the many borough Partnership Board / ICP / sub-committee pages on the same domain. Coverage ~2022 through current 2026 meetings.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>/board-meetings/north-east-london-icb-board-meeting-{N}/;/download-attachment/{id};'NHS North East London ICB Board - {DD Month YYYY}'</t>
+          <t>'NHS North East London ICB Board';/events/board-meetings-and-papers-;'papers pack';wp-content/uploads/&lt;year&gt;/ PDF packs</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Sub-committee;Partnership Board;Primary Care Contracts;Health and Care Board</t>
+          <t>Integrated Care Partnership / ICP papers pack;Partnership Board;Primary Care Contracts Sub-committee;borough boards (Newham/Waltham Forest/Tower Hamlets/Barking &amp; Dagenham);Health &amp; Wellbeing Board</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>NE London ICB board meetings &amp; papers page live; per-meeting packs via /download-attachment; papers publish 5 working days before meeting.</t>
+          <t>Confirmed canonical 'Board meetings and papers' page for NHS North East London ICB; per-meeting event pages carry the actual board-pack PDFs (verified an event page exposing a dated 'NHS North East London ICB Board' PDF pack).</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>New W&amp;NL site live from 1 April 2026 (merger of NW London + North Central London). The board-meetings page lists ICB Board of Members dates (1 Apr, 17 Jun, 22 Jul, 23 Sep AGM, 21 Oct 2026, 27 Jan, 24 Mar 2027) and links to the papers via the document library at /how-we-are-run/policies-and-publications/navigate/479/2410 (folder 'Board meetings in public'). WebFetch sees the library shell but NOT the folder contents (JS-rendered) — use Playwright to open each per-meeting date folder where the individual PDFs live (agenda, appointments paper, constitution, governance, SFIs etc.), each served from /download_file/{uuid}/{n}. Predecessor packs are at nclhealthandcare.org.uk and nwlondonicb.nhs.uk but the live on-domain source is the document library. Board meets quarterly. Exclude the '29 June 2026 PCCG' folder (Primary Care Commissioning Group, not the Board) and the ICP.</t>
+          <t>This is the correct ICB Board landing (not ICP). It lists upcoming/recent dated board meetings and points to the 'policies-and-publications' document library at /how-we-are-run/policies-and-publications/navigate/479/2410#document-library-2410 where each meeting has a dated folder ('Board meetings in public' then 1 April 2026, 17 June 2026, 22 July 2026, 21 October 2026). Open the meetings landing, follow the document-library link, then expand each dated folder to reach PDFs. Static fetch renders folder titles but NOT the PDF hrefs, so Playwright is needed. New post-April-2026 ICB, so it also carries legacy archives for predecessor bodies (North Central London ICB, North West London ICB) - prefer the 'West and North London ICB' 2026 dated folders. Coverage 2026 onward on the new-body archive.</t>
         </is>
       </c>
       <c r="N26" t="b">
@@ -2321,27 +2321,27 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>/how-we-are-run/policies-and-publications/navigate/479/2410 (Board meetings in public folder);per-meeting date subfolders e.g. /navigate/480/2410 = 1 April 2026;individual PDFs at /download_file/{uuid}/{n};'{YYYY.MM.DD} West and North London ICB Board ...'</t>
+          <t>'board meetings in public';dated folder names (e.g. '17 June 2026');document-library-2410;'W+NL Board';navigate/479/2410</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;PCCG;Primary Care Commissioning;Primary Care and Medicines Optimisation Committee;Committee</t>
+          <t>North Central London ICB previous meetings;North West London ICB previous meetings;ICP / Integrated Care Partnership;AGM-only entries</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>W&amp;NL ICB board meetings page live (dates to Mar 2027); papers in JS-rendered document library - needs browser.</t>
+          <t>Page lists dated W&amp;NL ICB Board meetings (1 Apr, 17 Jun, 22 Jul, 21 Oct 2026) and links to a document library with dated board-pack folders, but the actual PDFs sit behind a JS-rendered doc library so static fetch shows folders not PDF links.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Fetch this page directly (WebFetch works, no WAF). It is the Thames Valley ICB board papers listing; each entry is a single combined 'Public Board pack' PDF named 'Thames Valley ICB Board papers from {Month YYYY}' with a download link. Newest present is May 2026 (pack dated 13 May 2026 for the 20 May 2026 meeting). Grab the top/most-recent PDF. This is the ICB Board; do not confuse with any committee pages elsewhere under /how-we-make-decisions/.</t>
+          <t>This is the correct NHS Thames Valley (new post-April-2026 ICB) board-papers archive and it is the ICB Board (not ICP). The page renders dated board-pack entries with direct downloadable PDFs server-side, so static fetch works and no Playwright is needed. A crawler reads this page and collects the 'Thames Valley ICB Board papers &lt;date&gt;' PDF links. Brand-new ICB so coverage starts 2026 (currently 20 May 2026 and 15 July 2026), growing as meetings occur; the newest pack is flagged 'New'.</t>
         </is>
       </c>
       <c r="N29" t="b">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>'Thames Valley ICB Board papers from {Month YYYY}';single combined Public Board pack PDF per meeting</t>
+          <t>'Thames Valley ICB Board papers &lt;date&gt;';/board-papers/nhs-thames-valley-icb;MB file-size + download-count annotations;'New' badge on latest</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ICP;Integrated Care Partnership;Committee;Joint Committee</t>
+          <t>ICP / Integrated Care Partnership;predecessor BOB ICB (Buckinghamshire Oxfordshire Berkshire West) legacy papers;committee papers</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Thames Valley ICB board papers listing live; latest 20 May 2026 combined public board pack.</t>
+          <t>Static fetch returned two dated 2026 ICB board-pack PDFs directly on the page ('Thames Valley ICB Board papers 15 July 2026', 10.50 MB, marked New; and '20 May 2026', 2.81 MB).</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Static WebFetch works - no JS. The landing lists upcoming ICB Board dates and links the current/most-recent public board pack as a single PDF under /media/, plus a 'Previous Board meetings' sub-page (/about-us/corporate-information/governance/meetings-and-agendas/previous-board-meetings/) for the historical archive. This is the ICB Board (not ICP). Read the main page for the latest pack and follow the previous-meetings link for prior packs. Deep validator flagged it because only one PDF is exposed on the top page at a time.</t>
+          <t>The dedicated 'Integrated Care Board meetings' sub-page is ICB-Board-specific (the parent /meetings-and-agendas/ hub fans out to ICB / ICP / AGM categories -- prefer this ICB sub-page). It lists the next/most-recent meeting with a combined board PDF pack and a link to '.../previous-board-meetings/' for the archive. Fully static HTML -- WebFetch resolves everything, no Playwright. Each historic meeting has its own dated sub-page (slug 'board-meeting-held-in-public-on-&lt;weekday&gt;-&lt;d-month-yyyy&gt;') listing individual item PDFs on media.nhs.net; recent meetings also expose a single combined 'YYYYMMDD-public-board-pdf-pack.pdf' on the org /media/ path. Filter to the ICB Board -- skip the Integrated Care Partnership and AGM categories and committee minutes appearing as agenda items within a pack.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>/media/ path;filename YYYYMMDD-public-board-pdf-pack.pdf;'public board';'Board Papers'</t>
+          <t>combined 'YYYYMMDD-public-board-pdf-pack.pdf' on northeastnorthcumbria.nhs.uk/media/&lt;hash&gt;/;historic per-date sub-pages under /previous-board-meetings/;individual item PDFs on media.nhs.net/media/&lt;hash&gt;/item-NN-...pdf;meetings bi-monthly</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>integrated care partnership;ICP;committee;sub-committee</t>
+          <t>Integrated Care Partnership meetings;Annual General Meeting;committee minutes within pack (Audit, Finance/FPIC, Quality &amp; Safety/QSC, Executive);ICP Board</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Page hosts a dated ICB board pack (16 June 2026) plus a 'Previous Board meetings' archive link, so the current URL is live and correct.</t>
+          <t>Landing verified on own domain (heading 'Integrated Care Board meetings'), links dated 2025-2026 meetings and a confirmed 16 Jun 2026 public board PDF pack.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Static WebFetch works. The landing (herefordshireandworcestershire.icb.nhs.uk/meetings/board-papers) renders the itemised agenda for the next/most-recent public board meeting, but the individual document files are hosted on the cluster/partner domain www.hwics.org.uk via /download_file/{id} URLs (H&amp;W is clustered with Coventry &amp; Warwickshire; the 15 July 2026 pack is a joint 'in common' board carrying both CW and HW annual reports). This is acceptable and is the ICB Board (not ICP). Scrape the .icb.nhs.uk/meetings/board-papers page for agenda item links, which resolve to hwics.org.uk download URLs. Coverage 2026; prior meetings reachable from the same meetings area. Prefer this H&amp;W ICB page as the entry point.</t>
+          <t>The ICB site is a static server-rendered front-end; WebFetch works, no Playwright. /meetings/board-papers holds the NEXT meeting's pack; /meetings/past-board-papers is the dated archive (back to 2022, each date a heading with its PDF list). Board meets bi-monthly (odd months). All PDF hrefs point at the sister domain www.hwics.org.uk via /download_file/&lt;id&gt;/&lt;collection&gt; -- collection 414 = current pack, 463 = past-papers archive (numeric endpoints, not .pdf-suffixed). Single-ICB board, no ICP/Joint pages intermixed on these two pages; AGM material is bundled into the July board pack -- treat as ICB Board. Prefer /meetings/board-papers for the imminent pack and /meetings/past-board-papers to backfill.</t>
         </is>
       </c>
       <c r="N12" t="b">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>'Public Board';'Agenda 0x';hwics.org.uk/download_file/;'CEO report';'BAF';'Financial Report'</t>
+          <t>landing heading 'Board papers' with meeting date e.g. 'Wednesday 15 July 2026';past archive groups PDFs under date headings;PDF links www.hwics.org.uk/download_file/&lt;id&gt;/&lt;collection&gt; (414 current, 463 archive);agenda-item filenames like 'Agenda 09 CEO report','Agenda 14 BAF'</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>integrated care partnership;ICP;committee escalation-only;place-based</t>
+          <t>/download_file/force/&lt;id&gt;/463 pre-2023 forced-download links;committee/ICP/Joint content (not on these pages);XLSX governance-log attachments</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Page lists a full dated agenda for the 15 July 2026 public ICB Board (CEO report, finance, BAF, annual reports), confirming a live board-papers archive at the current URL.</t>
+          <t>Current board-papers page (15 Jul 2026 AGM+Board pack) and past-papers archive (May 2026 back to 2022) resolve with dated 2025-2026 packs on hwics.org.uk.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>This is the correct ICB Board landing (explicitly the ICB, not ICP). The main page lists dated board meetings (roughly every other month) but the PDFs are not on the landing itself - each date links to an individual event page under /events/board-meetings-and-papers-&lt;n&gt;/ which hosts the dated board-pack PDF. Scrape the landing for dated meeting links, follow each into its event page, then grab the PDF pack. Static fetch of the event pages does expose the PDF, so Playwright is not strictly required, though the landing's date links must be followed. Exclude the many borough Partnership Board / ICP / sub-committee pages on the same domain. Coverage ~2022 through current 2026 meetings.</t>
+          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2118,27 +2118,27 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>'NHS North East London ICB Board';/events/board-meetings-and-papers-;'papers pack';wp-content/uploads/&lt;year&gt;/ PDF packs</t>
+          <t>/wp-content/uploads/YYYY/MM/NHS-North-East-London-ICB-Board-DD.MM.YYYY*.pdf main pack;/download-attachment/NNNNN links on each event page;event pages /board-meetings/north-east-london-icb-board-meeting-NN/;supporting YYYY-MM-ICB-Board-questions-log.pdf</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Integrated Care Partnership / ICP papers pack;Partnership Board;Primary Care Contracts Sub-committee;borough boards (Newham/Waltham Forest/Tower Hamlets/Barking &amp; Dagenham);Health &amp; Wellbeing Board</t>
+          <t>Integrated-Care-Partnership / NEL-ICP packs (ICP not ICB);partnership-board-meetings-and-papers (borough boards);*-icb-sub-committee;Health-Wellbeing / Health-Care-Partnership boards</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Confirmed canonical 'Board meetings and papers' page for NHS North East London ICB; per-meeting event pages carry the actual board-pack PDFs (verified an event page exposing a dated 'NHS North East London ICB Board' PDF pack).</t>
+          <t>Landing verified on own domain with ICB name in title and dated 2025-2026 ICB Board entries; multiple full 2025 board packs downloaded and confirmed.</t>
         </is>
       </c>
     </row>
@@ -2313,35 +2313,35 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>This is the correct ICB Board landing (not ICP). It lists upcoming/recent dated board meetings and points to the 'policies-and-publications' document library at /how-we-are-run/policies-and-publications/navigate/479/2410#document-library-2410 where each meeting has a dated folder ('Board meetings in public' then 1 April 2026, 17 June 2026, 22 July 2026, 21 October 2026). Open the meetings landing, follow the document-library link, then expand each dated folder to reach PDFs. Static fetch renders folder titles but NOT the PDF hrefs, so Playwright is needed. New post-April-2026 ICB, so it also carries legacy archives for predecessor bodies (North Central London ICB, North West London ICB) - prefer the 'West and North London ICB' 2026 dated folders. Coverage 2026 onward on the new-body archive.</t>
+          <t>Newly merged ICB (April 2026, ex-North West London / Z9B2Z). The board-meetings landing (/how-we-are-run/meetings/w-plus-nl-board-meetings) is static HTML and lists upcoming ICB Board-of-Members dates plus a section linking into the document library at /how-we-are-run/policies-and-publications/navigate/{id}/2410. That library groups papers into per-meeting folders (1 Apr 2026, 17 Jun 2026, 22 Jul 2026, ...); each folder lists individual /download_file/{uuid}/{n} PDFs. Filter to the ICB Board of Members -- SKIP the PCCG folder, the ICP pages, and the Primary Care Commissioning Committee. First packs already fully populated (22 Jul 2026 pack has 13 papers). Static WebFetch is sufficient.</t>
         </is>
       </c>
       <c r="N26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>'board meetings in public';dated folder names (e.g. '17 June 2026');document-library-2410;'W+NL Board';navigate/479/2410</t>
+          <t>/download_file/{uuid}/{n} PDF endpoints;per-meeting folders under /how-we-are-run/policies-and-publications/navigate/{id}/2410;document titles prefixed with agenda-order numbers e.g. '00) 2026.07.22 WNL Board meeting in public agenda';papers published ~1 week before each meeting</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>North Central London ICB previous meetings;North West London ICB previous meetings;ICP / Integrated Care Partnership;AGM-only entries</t>
+          <t>PCCG / Primary Care Commissioning &amp; Contracting Group folders;Primary Care Commissioning Committee;ICP pages (/how-we-are-run/about-icp);legacy NCL/NWL pre-merger links;watch-live / YouTube recording links</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Page lists dated W&amp;NL ICB Board meetings (1 Apr, 17 Jun, 22 Jul, 21 Oct 2026) and links to a document library with dated board-pack folders, but the actual PDFs sit behind a JS-rendered doc library so static fetch shows folders not PDF links.</t>
+          <t>Full 13-document 22 July 2026 ICB Board pack is live on the org domain via /download_file links.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>This is the correct NHS Thames Valley (new post-April-2026 ICB) board-papers archive and it is the ICB Board (not ICP). The page renders dated board-pack entries with direct downloadable PDFs server-side, so static fetch works and no Playwright is needed. A crawler reads this page and collects the 'Thames Valley ICB Board papers &lt;date&gt;' PDF links. Brand-new ICB so coverage starts 2026 (currently 20 May 2026 and 15 July 2026), growing as meetings occur; the newest pack is flagged 'New'.</t>
+          <t>Newly merged ICB (established 1 April 2026 from Frimley + BOB). Static Joomla site (numeric-ID /file links) -- no Playwright. The board-papers category index links to two sub-pages: 'NHS Thames Valley ICB' (current, dated packs) and 'Pre-NHS Thames Valley archive' (legacy BOB/Frimley). This URL points straight to the current-ICB sub-page where the live 2026 packs are listed as single consolidated PDFs. Prefer this sub-page; skip the pre-TV archive and Joint Committee / ICP items. Packs are genuinely sparse -- this is the merged board's first months (first public meeting 20 May 2026, then 15 July 2026), so only two packs exist so far, which is expected not a scan failure.</t>
         </is>
       </c>
       <c r="N29" t="b">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>'Thames Valley ICB Board papers &lt;date&gt;';/board-papers/nhs-thames-valley-icb;MB file-size + download-count annotations;'New' badge on latest</t>
+          <t>sub-page /nhs-thames-valley-icb lists packs as single consolidated PDFs;URL pattern &lt;sub-page&gt;/&lt;numericID&gt;-thames-valley-icb-board-papers-&lt;DD-month-YYYY&gt;/file;titles 'Thames Valley ICB Board papers &lt;date&gt;';meeting dates so far: 20 May 2026, 15 July 2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>ICP / Integrated Care Partnership;predecessor BOB ICB (Buckinghamshire Oxfordshire Berkshire West) legacy papers;committee papers</t>
+          <t>pre-nhs-thames-valley-archive (legacy BOB/Frimley 2022-2025);nhs-bob-icb-board-meetings-* and nhs-frimley-icb-* paths;ICP / Joint Committee items</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Static fetch returned two dated 2026 ICB board-pack PDFs directly on the page ('Thames Valley ICB Board papers 15 July 2026', 10.50 MB, marked New; and '20 May 2026', 2.81 MB).</t>
+          <t>Two consolidated 2026 board packs (15 July 2026, 20 May 2026) confirmed on the current-ICB sub-page.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -756,7 +756,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The dedicated 'Integrated Care Board meetings' sub-page is ICB-Board-specific (the parent /meetings-and-agendas/ hub fans out to ICB / ICP / AGM categories -- prefer this ICB sub-page). It lists the next/most-recent meeting with a combined board PDF pack and a link to '.../previous-board-meetings/' for the archive. Fully static HTML -- WebFetch resolves everything, no Playwright. Each historic meeting has its own dated sub-page (slug 'board-meeting-held-in-public-on-&lt;weekday&gt;-&lt;d-month-yyyy&gt;') listing individual item PDFs on media.nhs.net; recent meetings also expose a single combined 'YYYYMMDD-public-board-pdf-pack.pdf' on the org /media/ path. Filter to the ICB Board -- skip the Integrated Care Partnership and AGM categories and committee minutes appearing as agenda items within a pack.</t>
+          <t>KEEP this URL - it holds no PDFs itself but it is the only page carrying BOTH the forward meeting schedule AND a link to the current/next meeting's own page where the pack lands, so it works as a one-hop hub. Repointing to /previous-board-meetings/ would blind a crawler to upcoming packs. Strategy: fetch the landing, follow any href matching board-meeting-held-in-public-* for the current pack, and separately follow /previous-board-meetings/ (24 dated links, July 2022 to March 2026) for backfill. Each per-meeting page carries 23-46 SEPARATE /media/{8-char-hash}/item-NN-*.pdf files - there is NO consolidated board pack, so a pack analyser must pull them all. Slugs are unguessable: the weekday is embedded inconsistently (...on-wednesday-29-july-2026, ...on-tuesday-31-march-2026, ...tuesday-25-march-2025 with no 'on', ...28-november-2023 with no weekday) - always scrape hrefs, never construct them. Filter on the board-meeting-held-in-public- prefix to isolate the ICB Board: the ICP lives under /previous-integrated-care-partnership-icp-meetings/ and AGMs under /annual-general-meetings/, and the 29 July 2026 AGM ran immediately before the Board on the same day. Beware: extraordinary board meetings (16 June 2026, 12 February 2026) are never archived - they surface only as draft-minutes items inside the next ordinary pack. Umbraco CMS, plain server-rendered HTML, no JS and no anti-bot; sitemap.xml 404s.</t>
         </is>
       </c>
       <c r="N5" t="b">
@@ -764,17 +764,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>combined 'YYYYMMDD-public-board-pdf-pack.pdf' on northeastnorthcumbria.nhs.uk/media/&lt;hash&gt;/;historic per-date sub-pages under /previous-board-meetings/;individual item PDFs on media.nhs.net/media/&lt;hash&gt;/item-NN-...pdf;meetings bi-monthly</t>
+          <t>item-NN numbered agenda PDFs;CEO Board Report;Finance update;BAF;board-meeting-held-in-public- slug</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Integrated Care Partnership meetings;Annual General Meeting;committee minutes within pack (Audit, Finance/FPIC, Quality &amp; Safety/QSC, Executive);ICP Board</t>
+          <t>ICP / Integrated Care Partnership meetings;Annual General Meeting papers;draft minutes of prior meetings</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Landing verified on own domain (heading 'Integrated Care Board meetings'), links dated 2025-2026 meetings and a confirmed 16 Jun 2026 public board PDF pack.</t>
+          <t>Landing confirmed live as a hub; the 29 July 2026 meeting page is live with 23+ item PDFs, and 31 March 2026 (33 PDFs) and 25 November 2025 (46 PDFs) are archived. Individual 2026 item PDFs verified as application/pdf.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Current board-papers page (15 Jul 2026 AGM+Board pack) and past-papers archive (May 2026 back to 2022) resolve with dated 2025-2026 packs on hwics.org.uk.</t>
+          <t>Board-papers page live with the full 15 July 2026 AGM and ICB Board pack (14 numbered agenda documents including CEO report, BAF, finance and quality).</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Landing verified on own domain with ICB name in title and dated 2025-2026 ICB Board entries; multiple full 2025 board packs downloaded and confirmed.</t>
+          <t>Landing live listing bi-monthly ICB Board dates with per-meeting event pages holding the packs; papers stated to publish a minimum of five working days before each meeting.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Full 13-document 22 July 2026 ICB Board pack is live on the org domain via /download_file links.</t>
+          <t>Landing live listing the 22 July 2026 board meeting with agenda papers (document library at /how-we-are-run/policies-and-publications/navigate/486/2410) and recording, plus 17 June 2026 and forward dates through March 2027.</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Two consolidated 2026 board packs (15 July 2026, 20 May 2026) confirmed on the current-ICB sub-page.</t>
+          <t>Current-ICB sub-page live with two consolidated 2026 packs: 15 July 2026 (10.5MB) and 20 May 2026 (2.8MB).</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Landing confirmed live as a hub; the 29 July 2026 meeting page is live with 23+ item PDFs, and 31 March 2026 (33 PDFs) and 25 November 2025 (46 PDFs) are archived. Individual 2026 item PDFs verified as application/pdf.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the hub lists the 29 July 2026 AGM/Board with its own 'Board meeting held in public on Wednesday 29 July 2026' page, forward dates 30 Sep 2026, 27 Jan and 31 Mar 2027, and the 'Previous Board meetings' archive. papers_partial is expected -- the hub holds no PDFs itself, by design.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Board-papers page live with the full 15 July 2026 AGM and ICB Board pack (14 numbered agenda documents including CEO report, BAF, finance and quality).</t>
+          <t>Re-verified 2026-08-01 via WebFetch: /meetings/board-papers carries the 15 July 2026 AGM + Board pack as ~15 separate documents (agenda, CEO report, governance log, quality/performance, finance, maternity, annual reports) with 'Past Board Papers' linked in the Meetings menu. no_papers_visible is a false negative from the /download_file/&lt;id&gt;/&lt;collection&gt; handler on the hwics.org.uk sister domain.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees.</t>
+          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees. Flag 2026-08-01: the landing's meeting list showed nothing later than 31 March 2026 on this run -- if a crawler finds no current pack here, check the /events/ pages directly before assuming a fetch failure.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Landing live listing bi-monthly ICB Board dates with per-meeting event pages holding the packs; papers stated to publish a minimum of five working days before each meeting.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the landing is live and per-meeting event pages still resolve with their packs, but the meeting list rendered no date later than 31 March 2026 on this run, so the published schedule appears not to have been updated for the current year. URL correct; the staleness is on the ICB's side and is worth a human look.</t>
         </is>
       </c>
     </row>
@@ -2176,11 +2176,15 @@
           <t>https://www.selondonics.org</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SEL-SWL</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Six borough place committees (Lambeth, Southwark, Lewisham, Greenwich, Bromley, Bexley) publish separately</t>
+          <t>Six borough place committees (Lambeth, Southwark, Lewisham, Greenwich, Bromley, Bexley) publish separately | Clustered with the other London ICB under joint chair Sir Richard Douglas and shared chief executive Andrew Bland; formal clustering agreed December 2025, appointments February 2026. Source: SWL ICB Annual Report 2025-26 and SWL board papers 15 July 2026.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -2225,9 +2229,17 @@
           <t>https://www.southwestlondon.icb.nhs.uk</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SEL-SWL</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Clustered with the other London ICB under joint chair Sir Richard Douglas and shared chief executive Andrew Bland; formal clustering agreed December 2025, appointments February 2026. Source: SWL ICB Annual Report 2025-26 and SWL board papers 15 July 2026.</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
@@ -2331,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2341,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Landing live listing the 22 July 2026 board meeting with agenda papers (document library at /how-we-are-run/policies-and-publications/navigate/486/2410) and recording, plus 17 June 2026 and forward dates through March 2027.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: landing links the 22 July 2026 board agenda and papers via the policies-and-publications document library and lists forward dates 23 Sep 2026 (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027; papers publish about a week ahead. no_papers_visible is a false negative -- the packs live in the document library one hop on.</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2566,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Current-ICB sub-page live with two consolidated 2026 packs: 15 July 2026 (10.5MB) and 20 May 2026 (2.8MB).</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the current-ICB sub-page lists consolidated packs 'Thames Valley ICB Board papers 15 July 2026' (10.5MB) and '20 May 2026' (2.8MB). papers_partial is a false negative from the numeric Joomla /file links.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the hub lists the 29 July 2026 AGM/Board with its own 'Board meeting held in public on Wednesday 29 July 2026' page, forward dates 30 Sep 2026, 27 Jan and 31 Mar 2027, and the 'Previous Board meetings' archive. papers_partial is expected -- the hub holds no PDFs itself, by design.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: the hub still works as recorded - forward schedule (29 Jul 2026 AGM+board, 30 Sep 2026, 27 Jan and 31 Mar 2027) plus a link to the current meeting's own agenda-and-documentation page. It holds no PDFs itself, hence papers_partial; keep the URL as the one-hop hub.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: /meetings/board-papers carries the 15 July 2026 AGM + Board pack as ~15 separate documents (agenda, CEO report, governance log, quality/performance, finance, maternity, annual reports) with 'Past Board Papers' linked in the Meetings menu. no_papers_visible is a false negative from the /download_file/&lt;id&gt;/&lt;collection&gt; handler on the hwics.org.uk sister domain.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: /meetings/board-papers holds the current 15 July 2026 AGM + ICB Board set (15 documents) and the nav links the dated archive at /meetings/past-board-papers. The no_papers_visible classification is a false negative - the landing carries only the current meeting.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the landing is live and per-meeting event pages still resolve with their packs, but the meeting list rendered no date later than 31 March 2026 on this run, so the published schedule appears not to have been updated for the current year. URL correct; the staleness is on the ICB's side and is worth a human look.</t>
+          <t>Re-verified 2026-08-08: the landing is live and remains the correct hub - the search index confirms a 15 July 2026 ICB board meeting and per-meeting pages under /board-meetings/ and /events/. Note a render quirk worth knowing: the 'upcoming meetings' block as fetched still shows the Sep 2024-Mar 2025 cycle, so a crawler should follow the per-meeting event pages rather than trusting that list.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: landing links the 22 July 2026 board agenda and papers via the policies-and-publications document library and lists forward dates 23 Sep 2026 (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027; papers publish about a week ahead. no_papers_visible is a false negative -- the packs live in the document library one hop on.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: landing is live with forward dates 23 Sep (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027, recent 22 Jul and 17 Jun 2026 meetings linked, and pointers into the document library plus the NCL/NWL predecessor archives. Papers sit in the library rather than on the landing, which is what produced no_papers_visible.</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the current-ICB sub-page lists consolidated packs 'Thames Valley ICB Board papers 15 July 2026' (10.5MB) and '20 May 2026' (2.8MB). papers_partial is a false negative from the numeric Joomla /file links.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: the current-ICB sub-page lists consolidated packs for 15 July 2026 (10.50 MB) and 20 May 2026 (2.81 MB); papers_partial reflects only the small number of packs published since the 1 April 2026 merger.</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Live page lists 2022-23 through 2025-26 board packs with direct PDF agenda/DOI/report links on the official docs subdomain.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: page is live (last reviewed 27 May 2026) with the 28 May 2026 extraordinary-meeting agenda and papers PDF plus fiscal-year archives back to 2022, all hosted on docs.cios.icb.nhs.uk. The validator's 'broken' classification did not reproduce - a fetch artefact.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,17 +774,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: the hub still works as recorded - forward schedule (29 Jul 2026 AGM+board, 30 Sep 2026, 27 Jan and 31 Mar 2027) plus a link to the current meeting's own agenda-and-documentation page. It holds no PDFs itself, hence papers_partial; keep the URL as the one-hop hub.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: hub page live carrying the forward schedule (29 Jul 2026 AGM, 30 Sep 2026, 27 Jan and 31 Mar 2027) plus the board-meeting-held-in-public-* link and the previous-board-meetings archive. It holds no PDFs itself, which is why the validator reports only a partial signal.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: /meetings/board-papers holds the current 15 July 2026 AGM + ICB Board set (15 documents) and the nav links the dated archive at /meetings/past-board-papers. The no_papers_visible classification is a false negative - the landing carries only the current meeting.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: /meetings/board-papers live carrying the 15 July 2026 AGM and Board pack as ~13 numbered agenda PDFs via www.hwics.org.uk/download_file/&lt;id&gt;/414; the Past Board Papers archive is still linked.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees. Flag 2026-08-01: the landing's meeting list showed nothing later than 31 March 2026 on this run -- if a crawler finds no current pack here, check the /events/ pages directly before assuming a fetch failure.</t>
+          <t>Static HTML landing renders fine via WebFetch (no Playwright). Lists ICB Board meeting dates every two months; each date links to a per-meeting event page at /board-meetings/north-east-london-icb-board-meeting-NN/ holding papers as /download-attachment/NNNNN links (the main board pack plus separate minutes/questions-log); underlying files live at /wp-content/uploads/YYYY/MM/. Papers publish at least 5 working days before each meeting, so the newest future date shows no PDFs until then. Filter to the NHS North East London ICB Board -- skip the ICP packs, borough Partnership Boards, Health &amp; Wellbeing boards, and named sub-committees. Flag 2026-08-01: the landing's meeting list showed nothing later than 31 March 2026 on this run -- if a crawler finds no current pack here, check the /events/ pages directly before assuming a fetch failure. Update 2026-08-15: the landing's own upcoming-meetings list is stale (newest entry 31 Mar 2026). The live index is /board-meetings/, which carries meeting 22 (14 May 2026) and meeting 23 (23 July 2026). Crawl /board-meetings/ for current packs and treat the landing as background only.</t>
         </is>
       </c>
       <c r="N23" t="b">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08: the landing is live and remains the correct hub - the search index confirms a 15 July 2026 ICB board meeting and per-meeting pages under /board-meetings/ and /events/. Note a render quirk worth knowing: the 'upcoming meetings' block as fetched still shows the Sep 2024-Mar 2025 cycle, so a crawler should follow the per-meeting event pages rather than trusting that list.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: landing live but its upcoming-meetings widget lags (newest entry 31 Mar 2026); the /board-meetings/ index is current, carrying meeting 22 (14 May 2026) and meeting 23 (23 July 2026). Crawlers should prefer /board-meetings/ over the landing's list.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: landing is live with forward dates 23 Sep (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027, recent 22 Jul and 17 Jun 2026 meetings linked, and pointers into the document library plus the NCL/NWL predecessor archives. Papers sit in the library rather than on the landing, which is what produced no_papers_visible.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: board-meetings landing live listing 17 Jun and 22 Jul 2026 plus the 23 Sep 2026 AGM, with papers in the document library at /policies-and-publications/navigate/486/2410 (previous meetings at /navigate/479/2410).</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: the current-ICB sub-page lists consolidated packs for 15 July 2026 (10.50 MB) and 20 May 2026 (2.81 MB); papers_partial reflects only the small number of packs published since the 1 April 2026 merger.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: NHS Thames Valley ICB board-papers sub-page live with consolidated packs for 20 May 2026 (2.81MB) and 15 July 2026 (10.5MB) via numeric /NNN-.../file links.</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: page is live (last reviewed 27 May 2026) with the 28 May 2026 extraordinary-meeting agenda and papers PDF plus fiscal-year archives back to 2022, all hosted on docs.cios.icb.nhs.uk. The validator's 'broken' classification did not reproduce - a fetch artefact.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Meetings in public page live; packs served from docs.cios.icb.nhs.uk including the 28 May 2026 extraordinary meeting. The local 403 was a WAF false positive.</t>
         </is>
       </c>
     </row>

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: hub page live carrying the forward schedule (29 Jul 2026 AGM, 30 Sep 2026, 27 Jan and 31 Mar 2027) plus the board-meeting-held-in-public-* link and the previous-board-meetings archive. It holds no PDFs itself, which is why the validator reports only a partial signal.</t>
+          <t>Re-verified 2026-08-22: the hub page carries no PDFs by design (papers_partial is expected here) but links one hop to 'Board meeting held in public on Wednesday 29 July 2026' and to the Previous Board meetings archive; forward dates 30 Sept 2026, 27 Jan and 31 Mar 2027.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: /meetings/board-papers live carrying the 15 July 2026 AGM and Board pack as ~13 numbered agenda PDFs via www.hwics.org.uk/download_file/&lt;id&gt;/414; the Past Board Papers archive is still linked.</t>
+          <t>Re-verified 2026-08-22: /meetings/board-papers holds the 15 July 2026 pack as 15 separate agenda-item PDFs on the hwics.org.uk download_file handler; 'Past Board Papers' archive link present.</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Previous Board Meetings page lists dated ICB Board / Board-in-Common agenda paper PDFs through April 2026 with recordings.</t>
+          <t>Landing validator 2026-08-22: papers_found - 11 dated PDFs, 0 year archives, 1 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Static fetch returned 'Showing 2 Publications filtered by ICB Board Meeting Papers' with two dated 2026 packs (Essex ICB Board Meeting Pack 23 April 2026 and 1 April 2026); the filter renders server-side.</t>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 0 year archives, 3 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: landing live but its upcoming-meetings widget lags (newest entry 31 Mar 2026); the /board-meetings/ index is current, carrying meeting 22 (14 May 2026) and meeting 23 (23 July 2026). Crawlers should prefer /board-meetings/ over the landing's list.</t>
+          <t>Re-verified 2026-08-22: the 29 July 2026 event page (/board-meetings/north-east-london-icb-board-meeting-23/) carries the 6MB 'NHS North East London ICB Board - 29 July 2026' pack plus an item-8.1 governance appendices pack. Note the landing renders meeting dates without years, which is why page summarisers misread the list as 2024.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: board-meetings landing live listing 17 Jun and 22 Jul 2026 plus the 23 Sep 2026 AGM, with papers in the document library at /policies-and-publications/navigate/486/2410 (previous meetings at /navigate/479/2410).</t>
+          <t>Re-verified 2026-08-22: landing lists the 22 July 2026 meeting with papers in the policies-and-publications document library plus a recording and a Q&amp;A response; forward dates 23 Sept 2026 (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027.</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: NHS Thames Valley ICB board-papers sub-page live with consolidated packs for 20 May 2026 (2.81MB) and 15 July 2026 (10.5MB) via numeric /NNN-.../file links.</t>
+          <t>Re-verified 2026-08-22: the sub-page lists 'Thames Valley ICB Board papers 15 July 2026' (10.50MB) and '20 May 2026' (2.81MB) - still only two packs, as expected for a board established 1 April 2026.</t>
         </is>
       </c>
     </row>
@@ -2710,9 +2710,21 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 1 year archives, 6 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">

--- a/icb_urls.xlsx
+++ b/icb_urls.xlsx
@@ -774,17 +774,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: the hub page carries no PDFs by design (papers_partial is expected here) but links one hop to 'Board meeting held in public on Wednesday 29 July 2026' and to the Previous Board meetings archive; forward dates 30 Sept 2026, 27 Jan and 31 Mar 2027.</t>
+          <t>2026-09-05: WebFetch reached the page; landing links the 29 July 2026 meeting sub-page plus a 'Previous Board meetings' archive - papers sit one hop deeper, which is why the validator scores it partial.</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: /meetings/board-papers holds the 15 July 2026 pack as 15 separate agenda-item PDFs on the hwics.org.uk download_file handler; 'Past Board Papers' archive link present.</t>
+          <t>2026-09-05: WebFetch reached the page; 15 documents for the 15 July 2026 public board, served as https://www.hwics.org.uk/download_file/{id}/414 links.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: landing lists the 22 July 2026 meeting with papers in the policies-and-publications document library plus a recording and a Q&amp;A response; forward dates 23 Sept 2026 (AGM), 21 Oct 2026, 27 Jan and 24 Mar 2027.</t>
+          <t>2026-09-05: WebFetch reached the page; newest entry 'Board meeting - 22 July 2026 - agenda papers' linking into the /navigate/486/2410 document library.</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: the sub-page lists 'Thames Valley ICB Board papers 15 July 2026' (10.50MB) and '20 May 2026' (2.81MB) - still only two packs, as expected for a board established 1 April 2026.</t>
+          <t>2026-09-05: WebFetch reached the page; newest 'Thames Valley ICB Board papers 15 July 2026' (10.5MB) served via the /file endpoint.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Meetings in public page live; packs served from docs.cios.icb.nhs.uk including the 28 May 2026 extraordinary meeting. The local 403 was a WAF false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; packs hosted on docs.cios.icb.nhs.uk with per-year archive sections, newest the 28 May 2026 extraordinary meeting.</t>
         </is>
       </c>
     </row>
